--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:16:11-03:00</t>
+    <t>2026-08-24T11:43:54-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T11:43:54-03:00</t>
+    <t>2026-09-15T15:40:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:40:41-03:00</t>
+    <t>2026-09-23T09:07:03-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:07:03-03:00</t>
+    <t>2026-09-30T18:22:16-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:22:16-03:00</t>
+    <t>2026-10-06T15:47:25-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4524" uniqueCount="733">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T15:47:25-03:00</t>
+    <t>2026-10-07T20:38:46-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -886,6 +886,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>Observation.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -935,6 +944,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>Observation.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -957,6 +972,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>Observation.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -2030,6 +2054,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -2614,7 +2642,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.20703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -6031,10 +6059,10 @@
         <v>138</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6061,13 +6089,11 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -6120,10 +6146,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6238,10 +6264,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6358,10 +6384,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6387,13 +6413,13 @@
         <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6443,7 +6469,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>93</v>
@@ -6478,10 +6504,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6507,10 +6533,10 @@
         <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6561,7 +6587,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6596,13 +6622,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>82</v>
@@ -6627,10 +6653,10 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>139</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6716,10 +6742,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6834,10 +6860,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6954,10 +6980,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6983,13 +7009,13 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6997,7 +7023,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -7039,7 +7065,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>93</v>
@@ -7074,10 +7100,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7100,13 +7126,13 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7157,7 +7183,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7192,13 +7218,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>275</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -7223,10 +7249,10 @@
         <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>139</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7253,13 +7279,11 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7312,10 +7336,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7430,10 +7454,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7550,10 +7574,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7579,13 +7603,13 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7593,7 +7617,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7635,7 +7659,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7670,10 +7694,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7699,10 +7723,10 @@
         <v>204</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7753,7 +7777,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7788,10 +7812,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7817,13 +7841,13 @@
         <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7831,7 +7855,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7873,7 +7897,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -7908,10 +7932,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7934,13 +7958,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7991,7 +8015,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8026,10 +8050,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8055,13 +8079,13 @@
         <v>228</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8111,7 +8135,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8120,7 +8144,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -8146,10 +8170,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8175,13 +8199,13 @@
         <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8207,13 +8231,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8231,7 +8255,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8266,10 +8290,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8295,13 +8319,13 @@
         <v>164</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8351,7 +8375,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8375,7 +8399,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8386,10 +8410,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8504,10 +8528,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8624,10 +8648,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8653,16 +8677,16 @@
         <v>113</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8690,10 +8714,10 @@
         <v>195</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8711,7 +8735,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8735,7 +8759,7 @@
         <v>136</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8746,10 +8770,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8775,16 +8799,16 @@
         <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8809,13 +8833,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8833,7 +8857,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8854,10 +8878,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8868,10 +8892,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8897,16 +8921,16 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8919,7 +8943,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -8955,7 +8979,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8976,10 +9000,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8990,10 +9014,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9019,13 +9043,13 @@
         <v>228</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9039,7 +9063,7 @@
         <v>82</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>82</v>
@@ -9075,7 +9099,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9096,10 +9120,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9110,10 +9134,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9136,13 +9160,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9193,7 +9217,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9214,10 +9238,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9228,10 +9252,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9254,16 +9278,16 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9313,7 +9337,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9334,10 +9358,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9348,10 +9372,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9377,13 +9401,13 @@
         <v>228</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9433,7 +9457,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9468,10 +9492,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9494,16 +9518,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9553,7 +9577,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9577,7 +9601,7 @@
         <v>223</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>264</v>
@@ -9588,14 +9612,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9614,19 +9638,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9675,7 +9699,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9690,19 +9714,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9710,14 +9734,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9736,19 +9760,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9797,7 +9821,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9812,19 +9836,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9832,10 +9856,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9950,10 +9974,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10070,14 +10094,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10099,10 +10123,10 @@
         <v>138</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>160</v>
@@ -10157,7 +10181,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10192,10 +10216,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10218,17 +10242,17 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10277,7 +10301,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10301,7 +10325,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10312,10 +10336,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10338,17 +10362,17 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10397,7 +10421,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10409,7 +10433,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10421,7 +10445,7 @@
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10432,10 +10456,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10550,10 +10574,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10670,10 +10694,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10696,13 +10720,13 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10753,7 +10777,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10777,7 +10801,7 @@
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10788,10 +10812,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10814,19 +10838,19 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10875,7 +10899,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10899,7 +10923,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10910,10 +10934,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10936,13 +10960,13 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10993,7 +11017,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11017,7 +11041,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11028,10 +11052,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11054,19 +11078,19 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11115,7 +11139,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11139,7 +11163,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11150,10 +11174,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11176,19 +11200,19 @@
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11237,7 +11261,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11261,7 +11285,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11272,10 +11296,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11301,10 +11325,10 @@
         <v>113</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11334,10 +11358,10 @@
         <v>195</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11355,7 +11379,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11379,7 +11403,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11390,10 +11414,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11416,13 +11440,13 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11430,7 +11454,7 @@
         <v>82</v>
       </c>
       <c r="Q74" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="R74" t="s" s="2">
         <v>82</v>
@@ -11475,7 +11499,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11499,7 +11523,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11510,10 +11534,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11536,13 +11560,13 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11593,7 +11617,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11617,7 +11641,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11628,10 +11652,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11654,13 +11678,13 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11711,7 +11735,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11735,7 +11759,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11746,10 +11770,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11772,13 +11796,13 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11829,7 +11853,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11853,7 +11877,7 @@
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11864,10 +11888,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11893,10 +11917,10 @@
         <v>113</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11926,10 +11950,10 @@
         <v>195</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11947,7 +11971,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11971,7 +11995,7 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11982,10 +12006,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12011,13 +12035,13 @@
         <v>113</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12047,7 +12071,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12065,7 +12089,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12100,10 +12124,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12126,16 +12150,16 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12185,7 +12209,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12220,10 +12244,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12249,16 +12273,16 @@
         <v>113</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12286,10 +12310,10 @@
         <v>195</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12307,7 +12331,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12331,7 +12355,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12342,10 +12366,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12368,13 +12392,13 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12425,7 +12449,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12449,7 +12473,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12460,10 +12484,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12489,13 +12513,13 @@
         <v>204</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12524,10 +12548,10 @@
         <v>195</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12545,7 +12569,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12569,7 +12593,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12580,10 +12604,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12606,16 +12630,16 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12665,7 +12689,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12686,13 +12710,13 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -12700,10 +12724,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12726,17 +12750,17 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12785,7 +12809,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12800,19 +12824,19 @@
         <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
@@ -12820,10 +12844,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12846,19 +12870,19 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12907,7 +12931,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12916,7 +12940,7 @@
         <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12925,27 +12949,27 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12971,16 +12995,16 @@
         <v>204</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13005,13 +13029,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -13029,7 +13053,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13038,7 +13062,7 @@
         <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>105</v>
@@ -13053,7 +13077,7 @@
         <v>136</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13064,14 +13088,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13093,16 +13117,16 @@
         <v>204</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13127,13 +13151,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13151,7 +13175,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13169,27 +13193,27 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13212,19 +13236,19 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13273,7 +13297,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13294,10 +13318,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13308,10 +13332,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13337,13 +13361,13 @@
         <v>204</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13372,10 +13396,10 @@
         <v>195</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13393,7 +13417,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13411,27 +13435,27 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13457,16 +13481,16 @@
         <v>204</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13494,10 +13518,10 @@
         <v>195</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13515,7 +13539,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13536,10 +13560,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13550,10 +13574,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13668,10 +13692,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13788,10 +13812,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13910,10 +13934,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14032,10 +14056,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14058,16 +14082,16 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14117,7 +14141,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14135,27 +14159,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14178,16 +14202,16 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14237,7 +14261,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14255,27 +14279,27 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14298,19 +14322,19 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14359,7 +14383,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14371,7 +14395,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14380,10 +14404,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14394,10 +14418,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14512,10 +14536,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14632,14 +14656,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14661,10 +14685,10 @@
         <v>138</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>160</v>
@@ -14719,7 +14743,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14754,10 +14778,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14780,13 +14804,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14837,7 +14861,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14846,10 +14870,10 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>105</v>
+        <v>656</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14858,10 +14882,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14872,10 +14896,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14898,13 +14922,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14955,7 +14979,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14964,10 +14988,10 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>105</v>
+        <v>656</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -14976,10 +15000,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14990,10 +15014,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15019,16 +15043,16 @@
         <v>204</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15056,10 +15080,10 @@
         <v>117</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15077,7 +15101,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15095,13 +15119,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15112,10 +15136,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15141,16 +15165,16 @@
         <v>204</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15175,13 +15199,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15199,7 +15223,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15217,13 +15241,13 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15234,10 +15258,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15260,17 +15284,17 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15319,7 +15343,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15343,7 +15367,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15354,10 +15378,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15383,10 +15407,10 @@
         <v>228</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15437,7 +15461,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15458,10 +15482,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15472,10 +15496,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15498,16 +15522,16 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15557,7 +15581,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15578,10 +15602,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15592,10 +15616,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15618,16 +15642,16 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15677,7 +15701,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15698,10 +15722,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>693</v>
+        <v>702</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15712,10 +15736,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15738,19 +15762,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15799,7 +15823,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15820,10 +15844,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15834,10 +15858,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15952,10 +15976,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16072,14 +16096,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16101,10 +16125,10 @@
         <v>138</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>160</v>
@@ -16159,7 +16183,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16194,10 +16218,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16223,13 +16247,13 @@
         <v>204</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>218</v>
@@ -16257,13 +16281,13 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16281,7 +16305,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>93</v>
@@ -16299,7 +16323,7 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>223</v>
@@ -16316,10 +16340,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16342,19 +16366,19 @@
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16403,7 +16427,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16421,27 +16445,27 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16467,16 +16491,16 @@
         <v>204</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16501,13 +16525,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16525,7 +16549,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16534,7 +16558,7 @@
         <v>93</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>105</v>
@@ -16549,7 +16573,7 @@
         <v>136</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16560,14 +16584,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16589,16 +16613,16 @@
         <v>204</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16623,13 +16647,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16647,7 +16671,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16665,27 +16689,27 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16711,16 +16735,16 @@
         <v>83</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16769,7 +16793,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16790,10 +16814,10 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T20:38:46-03:00</t>
+    <t>2026-10-08T20:36:58-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:36:58-03:00</t>
+    <t>2026-10-14T17:05:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T17:05:02-03:00</t>
+    <t>2026-10-19T10:41:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T10:41:45-03:00</t>
+    <t>2026-10-20T16:57:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:57:20-03:00</t>
+    <t>2026-10-21T08:58:18-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T08:58:18-03:00</t>
+    <t>2026-10-21T11:27:45-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-BRMedidaObservada.xlsx
+++ b/output/StructureDefinition-BRMedidaObservada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:27:45-03:00</t>
+    <t>2026-10-21T12:30:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
